--- a/artfynd/A 35369-2024 artfynd.xlsx
+++ b/artfynd/A 35369-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120495316</v>
+        <v>120493081</v>
       </c>
       <c r="B2" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375540</v>
+        <v>375570</v>
       </c>
       <c r="R2" t="n">
-        <v>6932499</v>
+        <v>6932549</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120494119</v>
+        <v>120495316</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375521</v>
+        <v>375540</v>
       </c>
       <c r="R3" t="n">
-        <v>6932485</v>
+        <v>6932499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120493081</v>
+        <v>120494119</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375570</v>
+        <v>375521</v>
       </c>
       <c r="R4" t="n">
-        <v>6932549</v>
+        <v>6932485</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120493033</v>
+        <v>120493849</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>105017</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375572</v>
+        <v>375571</v>
       </c>
       <c r="R6" t="n">
-        <v>6932556</v>
+        <v>6932464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120493849</v>
+        <v>120493033</v>
       </c>
       <c r="B7" t="n">
-        <v>105017</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375571</v>
+        <v>375572</v>
       </c>
       <c r="R7" t="n">
-        <v>6932464</v>
+        <v>6932556</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1909,7 +1909,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120495702</v>
+        <v>120495561</v>
       </c>
       <c r="B14" t="n">
         <v>74654</v>
@@ -1949,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>375606</v>
+        <v>375616</v>
       </c>
       <c r="R14" t="n">
-        <v>6932478</v>
+        <v>6932514</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2011,7 +2011,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120495561</v>
+        <v>120495702</v>
       </c>
       <c r="B15" t="n">
         <v>74654</v>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>375616</v>
+        <v>375606</v>
       </c>
       <c r="R15" t="n">
-        <v>6932514</v>
+        <v>6932478</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3352,10 +3352,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120495373</v>
+        <v>120494414</v>
       </c>
       <c r="B28" t="n">
-        <v>105017</v>
+        <v>91277</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3364,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>67</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>375540</v>
+        <v>375498</v>
       </c>
       <c r="R28" t="n">
-        <v>6932499</v>
+        <v>6932458</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120494304</v>
+        <v>120495373</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>105017</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,46 +3466,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>375499</v>
+        <v>375540</v>
       </c>
       <c r="R29" t="n">
-        <v>6932447</v>
+        <v>6932499</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3549,22 +3544,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120494414</v>
+        <v>120494304</v>
       </c>
       <c r="B30" t="n">
-        <v>91277</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3573,41 +3568,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>375498</v>
+        <v>375499</v>
       </c>
       <c r="R30" t="n">
-        <v>6932458</v>
+        <v>6932447</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3651,12 +3651,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 35369-2024 artfynd.xlsx
+++ b/artfynd/A 35369-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120493081</v>
+        <v>120493795</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375570</v>
+        <v>375623</v>
       </c>
       <c r="R2" t="n">
-        <v>6932549</v>
+        <v>6932500</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120495316</v>
+        <v>120493081</v>
       </c>
       <c r="B3" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375540</v>
+        <v>375570</v>
       </c>
       <c r="R3" t="n">
-        <v>6932499</v>
+        <v>6932549</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120494119</v>
+        <v>120493849</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>105017</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375521</v>
+        <v>375571</v>
       </c>
       <c r="R4" t="n">
-        <v>6932485</v>
+        <v>6932464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120495530</v>
+        <v>120494289</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375606</v>
+        <v>375501</v>
       </c>
       <c r="R5" t="n">
-        <v>6932534</v>
+        <v>6932488</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120493849</v>
+        <v>120494168</v>
       </c>
       <c r="B6" t="n">
-        <v>105017</v>
+        <v>74654</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375571</v>
+        <v>375521</v>
       </c>
       <c r="R6" t="n">
-        <v>6932464</v>
+        <v>6932485</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120493033</v>
+        <v>120495214</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,37 +1206,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375572</v>
+        <v>375522</v>
       </c>
       <c r="R7" t="n">
-        <v>6932556</v>
+        <v>6932476</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120494289</v>
+        <v>120493457</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375501</v>
+        <v>375571</v>
       </c>
       <c r="R8" t="n">
-        <v>6932488</v>
+        <v>6932496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120495214</v>
+        <v>120495391</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>375522</v>
+        <v>375548</v>
       </c>
       <c r="R9" t="n">
-        <v>6932476</v>
+        <v>6932525</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120494247</v>
+        <v>120494471</v>
       </c>
       <c r="B10" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,13 +1546,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>375521</v>
+        <v>375497</v>
       </c>
       <c r="R10" t="n">
-        <v>6932485</v>
+        <v>6932487</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,6 +1582,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,19 +1601,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120493668</v>
+        <v>120493210</v>
       </c>
       <c r="B11" t="n">
         <v>74654</v>
@@ -1643,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375574</v>
+        <v>375572</v>
       </c>
       <c r="R11" t="n">
-        <v>6932484</v>
+        <v>6932539</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120493210</v>
+        <v>120495425</v>
       </c>
       <c r="B12" t="n">
-        <v>74654</v>
+        <v>91023</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>375572</v>
+        <v>375548</v>
       </c>
       <c r="R12" t="n">
-        <v>6932539</v>
+        <v>6932515</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120495527</v>
+        <v>120495387</v>
       </c>
       <c r="B13" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1823,37 +1833,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>375606</v>
+        <v>375558</v>
       </c>
       <c r="R13" t="n">
-        <v>6932534</v>
+        <v>6932484</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1897,22 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120495561</v>
+        <v>120494304</v>
       </c>
       <c r="B14" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,37 +1940,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>375616</v>
+        <v>375499</v>
       </c>
       <c r="R14" t="n">
-        <v>6932514</v>
+        <v>6932447</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1999,22 +2019,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120495702</v>
+        <v>120495373</v>
       </c>
       <c r="B15" t="n">
-        <v>74654</v>
+        <v>105017</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2023,25 +2043,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>375606</v>
+        <v>375540</v>
       </c>
       <c r="R15" t="n">
-        <v>6932478</v>
+        <v>6932499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120493457</v>
+        <v>120495530</v>
       </c>
       <c r="B16" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2129,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2153,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>375571</v>
+        <v>375606</v>
       </c>
       <c r="R16" t="n">
-        <v>6932496</v>
+        <v>6932534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120494168</v>
+        <v>120493443</v>
       </c>
       <c r="B17" t="n">
         <v>74654</v>
@@ -2255,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>375521</v>
+        <v>375571</v>
       </c>
       <c r="R17" t="n">
-        <v>6932485</v>
+        <v>6932496</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120493795</v>
+        <v>120495561</v>
       </c>
       <c r="B18" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2333,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2357,13 +2377,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>375623</v>
+        <v>375616</v>
       </c>
       <c r="R18" t="n">
-        <v>6932500</v>
+        <v>6932514</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2407,22 +2427,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120494471</v>
+        <v>120494309</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2431,25 +2451,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2459,13 +2479,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>375497</v>
+        <v>375495</v>
       </c>
       <c r="R19" t="n">
-        <v>6932487</v>
+        <v>6932470</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2495,11 +2515,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2514,22 +2529,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120494003</v>
+        <v>120493668</v>
       </c>
       <c r="B20" t="n">
-        <v>91023</v>
+        <v>74654</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2538,25 +2553,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>375521</v>
+        <v>375574</v>
       </c>
       <c r="R20" t="n">
-        <v>6932485</v>
+        <v>6932484</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120494309</v>
+        <v>120493566</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2640,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2668,13 +2683,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>375495</v>
+        <v>375565</v>
       </c>
       <c r="R21" t="n">
-        <v>6932470</v>
+        <v>6932493</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2704,6 +2719,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,22 +2738,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120495387</v>
+        <v>120494414</v>
       </c>
       <c r="B22" t="n">
-        <v>57320</v>
+        <v>91277</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2742,46 +2762,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>375558</v>
+        <v>375498</v>
       </c>
       <c r="R22" t="n">
-        <v>6932484</v>
+        <v>6932458</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2825,22 +2840,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120495401</v>
+        <v>120494247</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2853,21 +2868,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2877,13 +2892,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>375558</v>
+        <v>375521</v>
       </c>
       <c r="R23" t="n">
-        <v>6932484</v>
+        <v>6932485</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2927,22 +2942,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120495391</v>
+        <v>120495401</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2955,42 +2970,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>375548</v>
+        <v>375558</v>
       </c>
       <c r="R24" t="n">
-        <v>6932525</v>
+        <v>6932484</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3034,12 +3044,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3148,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120493443</v>
+        <v>120494003</v>
       </c>
       <c r="B26" t="n">
-        <v>74654</v>
+        <v>91023</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3170,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>1209</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>375571</v>
+        <v>375521</v>
       </c>
       <c r="R26" t="n">
-        <v>6932496</v>
+        <v>6932485</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3260,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120493223</v>
+        <v>120493340</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3266,21 +3276,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,13 +3300,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>375572</v>
+        <v>375567</v>
       </c>
       <c r="R27" t="n">
-        <v>6932539</v>
+        <v>6932508</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3340,22 +3350,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120494414</v>
+        <v>120493033</v>
       </c>
       <c r="B28" t="n">
-        <v>91277</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3364,25 +3374,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3392,10 +3402,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>375498</v>
+        <v>375572</v>
       </c>
       <c r="R28" t="n">
-        <v>6932458</v>
+        <v>6932556</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3454,10 +3464,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120495373</v>
+        <v>120494119</v>
       </c>
       <c r="B29" t="n">
-        <v>105017</v>
+        <v>90580</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3466,25 +3476,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3494,10 +3504,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>375540</v>
+        <v>375521</v>
       </c>
       <c r="R29" t="n">
-        <v>6932499</v>
+        <v>6932485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3556,10 +3566,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120494304</v>
+        <v>120495527</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3572,42 +3582,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>375499</v>
+        <v>375606</v>
       </c>
       <c r="R30" t="n">
-        <v>6932447</v>
+        <v>6932534</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3651,22 +3656,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120493340</v>
+        <v>120493223</v>
       </c>
       <c r="B31" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3679,21 +3684,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,13 +3708,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>375567</v>
+        <v>375572</v>
       </c>
       <c r="R31" t="n">
-        <v>6932508</v>
+        <v>6932539</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3753,22 +3758,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120495425</v>
+        <v>120495702</v>
       </c>
       <c r="B32" t="n">
-        <v>91023</v>
+        <v>74654</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3777,25 +3782,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3805,10 +3810,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>375548</v>
+        <v>375606</v>
       </c>
       <c r="R32" t="n">
-        <v>6932515</v>
+        <v>6932478</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3867,10 +3872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120493566</v>
+        <v>120495316</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3883,21 +3888,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3907,13 +3912,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>375565</v>
+        <v>375540</v>
       </c>
       <c r="R33" t="n">
-        <v>6932493</v>
+        <v>6932499</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3943,11 +3948,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3962,12 +3962,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 35369-2024 artfynd.xlsx
+++ b/artfynd/A 35369-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120493795</v>
+        <v>120493223</v>
       </c>
       <c r="B2" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375623</v>
+        <v>375572</v>
       </c>
       <c r="R2" t="n">
-        <v>6932500</v>
+        <v>6932539</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,19 +765,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120493081</v>
+        <v>120493566</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375570</v>
+        <v>375565</v>
       </c>
       <c r="R3" t="n">
-        <v>6932549</v>
+        <v>6932493</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120493849</v>
+        <v>120494309</v>
       </c>
       <c r="B4" t="n">
-        <v>105017</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221725</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>375571</v>
+        <v>375495</v>
       </c>
       <c r="R4" t="n">
-        <v>6932464</v>
+        <v>6932470</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120494289</v>
+        <v>120493443</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>375501</v>
+        <v>375571</v>
       </c>
       <c r="R5" t="n">
-        <v>6932488</v>
+        <v>6932496</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120494168</v>
+        <v>120495214</v>
       </c>
       <c r="B6" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,37 +1104,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>375521</v>
+        <v>375522</v>
       </c>
       <c r="R6" t="n">
-        <v>6932485</v>
+        <v>6932476</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120495214</v>
+        <v>120493340</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,42 +1211,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>375522</v>
+        <v>375567</v>
       </c>
       <c r="R7" t="n">
-        <v>6932476</v>
+        <v>6932508</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,22 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120493457</v>
+        <v>120494471</v>
       </c>
       <c r="B8" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,13 +1337,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>375571</v>
+        <v>375497</v>
       </c>
       <c r="R8" t="n">
-        <v>6932496</v>
+        <v>6932487</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1373,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1387,22 +1392,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120495391</v>
+        <v>120494497</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,42 +1420,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>375548</v>
+        <v>375501</v>
       </c>
       <c r="R9" t="n">
-        <v>6932525</v>
+        <v>6932488</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120494471</v>
+        <v>120493033</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>375497</v>
+        <v>375572</v>
       </c>
       <c r="R10" t="n">
-        <v>6932487</v>
+        <v>6932556</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1582,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1601,22 +1596,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120493210</v>
+        <v>120495387</v>
       </c>
       <c r="B11" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,37 +1624,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>375572</v>
+        <v>375558</v>
       </c>
       <c r="R11" t="n">
-        <v>6932539</v>
+        <v>6932484</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,22 +1703,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120495425</v>
+        <v>120494304</v>
       </c>
       <c r="B12" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,41 +1727,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>375548</v>
+        <v>375499</v>
       </c>
       <c r="R12" t="n">
-        <v>6932515</v>
+        <v>6932447</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1805,22 +1810,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120495387</v>
+        <v>120494247</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,42 +1838,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>375558</v>
+        <v>375521</v>
       </c>
       <c r="R13" t="n">
-        <v>6932484</v>
+        <v>6932485</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1912,22 +1912,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120494304</v>
+        <v>120495702</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,42 +1940,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>375499</v>
+        <v>375606</v>
       </c>
       <c r="R14" t="n">
-        <v>6932447</v>
+        <v>6932478</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2019,22 +2014,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120495373</v>
+        <v>120495561</v>
       </c>
       <c r="B15" t="n">
-        <v>105017</v>
+        <v>74654</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,25 +2038,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2071,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>375540</v>
+        <v>375616</v>
       </c>
       <c r="R15" t="n">
-        <v>6932499</v>
+        <v>6932514</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120495530</v>
+        <v>120493457</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2149,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2173,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>375606</v>
+        <v>375571</v>
       </c>
       <c r="R16" t="n">
-        <v>6932534</v>
+        <v>6932496</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120493443</v>
+        <v>120494119</v>
       </c>
       <c r="B17" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2251,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>375571</v>
+        <v>375521</v>
       </c>
       <c r="R17" t="n">
-        <v>6932496</v>
+        <v>6932485</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,7 +2332,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120495561</v>
+        <v>120493210</v>
       </c>
       <c r="B18" t="n">
         <v>74654</v>
@@ -2377,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>375616</v>
+        <v>375572</v>
       </c>
       <c r="R18" t="n">
-        <v>6932514</v>
+        <v>6932539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2439,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120494309</v>
+        <v>120494003</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>91023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>375495</v>
+        <v>375521</v>
       </c>
       <c r="R19" t="n">
-        <v>6932470</v>
+        <v>6932485</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,7 +2536,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120493668</v>
+        <v>120495527</v>
       </c>
       <c r="B20" t="n">
         <v>74654</v>
@@ -2581,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>375574</v>
+        <v>375606</v>
       </c>
       <c r="R20" t="n">
-        <v>6932484</v>
+        <v>6932534</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,7 +2638,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120493566</v>
+        <v>120494289</v>
       </c>
       <c r="B21" t="n">
         <v>78542</v>
@@ -2683,13 +2678,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>375565</v>
+        <v>375501</v>
       </c>
       <c r="R21" t="n">
-        <v>6932493</v>
+        <v>6932488</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2719,11 +2714,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2738,22 +2728,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120494414</v>
+        <v>120495425</v>
       </c>
       <c r="B22" t="n">
-        <v>91277</v>
+        <v>91023</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2766,21 +2756,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2790,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>375498</v>
+        <v>375548</v>
       </c>
       <c r="R22" t="n">
-        <v>6932458</v>
+        <v>6932515</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2852,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120494247</v>
+        <v>120495530</v>
       </c>
       <c r="B23" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2868,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2892,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>375521</v>
+        <v>375606</v>
       </c>
       <c r="R23" t="n">
-        <v>6932485</v>
+        <v>6932534</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2954,10 +2944,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120495401</v>
+        <v>120494168</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2970,21 +2960,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,13 +2984,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>375558</v>
+        <v>375521</v>
       </c>
       <c r="R24" t="n">
-        <v>6932484</v>
+        <v>6932485</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3044,19 +3034,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120494497</v>
+        <v>120493668</v>
       </c>
       <c r="B25" t="n">
         <v>74654</v>
@@ -3096,10 +3086,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>375501</v>
+        <v>375574</v>
       </c>
       <c r="R25" t="n">
-        <v>6932488</v>
+        <v>6932484</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3158,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120494003</v>
+        <v>120493849</v>
       </c>
       <c r="B26" t="n">
-        <v>91023</v>
+        <v>105017</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3170,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1209</v>
+        <v>221725</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3198,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>375521</v>
+        <v>375571</v>
       </c>
       <c r="R26" t="n">
-        <v>6932485</v>
+        <v>6932464</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3260,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120493340</v>
+        <v>120494414</v>
       </c>
       <c r="B27" t="n">
-        <v>90598</v>
+        <v>91277</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3272,25 +3262,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>67</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3300,13 +3290,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>375567</v>
+        <v>375498</v>
       </c>
       <c r="R27" t="n">
-        <v>6932508</v>
+        <v>6932458</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3350,22 +3340,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120493033</v>
+        <v>120493795</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3378,21 +3368,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3402,13 +3392,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>375572</v>
+        <v>375623</v>
       </c>
       <c r="R28" t="n">
-        <v>6932556</v>
+        <v>6932500</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3452,22 +3442,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120494119</v>
+        <v>120493081</v>
       </c>
       <c r="B29" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3480,21 +3470,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3504,13 +3494,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>375521</v>
+        <v>375570</v>
       </c>
       <c r="R29" t="n">
-        <v>6932485</v>
+        <v>6932549</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3540,6 +3530,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3554,19 +3549,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120495527</v>
+        <v>120495316</v>
       </c>
       <c r="B30" t="n">
         <v>74654</v>
@@ -3606,10 +3601,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>375606</v>
+        <v>375540</v>
       </c>
       <c r="R30" t="n">
-        <v>6932534</v>
+        <v>6932499</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3668,7 +3663,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120493223</v>
+        <v>120495401</v>
       </c>
       <c r="B31" t="n">
         <v>78542</v>
@@ -3708,13 +3703,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>375572</v>
+        <v>375558</v>
       </c>
       <c r="R31" t="n">
-        <v>6932539</v>
+        <v>6932484</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3758,22 +3753,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120495702</v>
+        <v>120495391</v>
       </c>
       <c r="B32" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3786,37 +3781,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>375606</v>
+        <v>375548</v>
       </c>
       <c r="R32" t="n">
-        <v>6932478</v>
+        <v>6932525</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120495316</v>
+        <v>120495373</v>
       </c>
       <c r="B33" t="n">
-        <v>74654</v>
+        <v>105017</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3884,25 +3884,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>

--- a/artfynd/A 35369-2024 artfynd.xlsx
+++ b/artfynd/A 35369-2024 artfynd.xlsx
@@ -2536,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120495527</v>
+        <v>120494289</v>
       </c>
       <c r="B20" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>375606</v>
+        <v>375501</v>
       </c>
       <c r="R20" t="n">
-        <v>6932534</v>
+        <v>6932488</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120494289</v>
+        <v>120495527</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>375501</v>
+        <v>375606</v>
       </c>
       <c r="R21" t="n">
-        <v>6932488</v>
+        <v>6932534</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2740,10 +2740,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120495425</v>
+        <v>120495530</v>
       </c>
       <c r="B22" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2752,25 +2752,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>375548</v>
+        <v>375606</v>
       </c>
       <c r="R22" t="n">
-        <v>6932515</v>
+        <v>6932534</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120495530</v>
+        <v>120495425</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2854,25 +2854,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>375606</v>
+        <v>375548</v>
       </c>
       <c r="R23" t="n">
-        <v>6932534</v>
+        <v>6932515</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,10 +3148,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120493849</v>
+        <v>120494414</v>
       </c>
       <c r="B26" t="n">
-        <v>105017</v>
+        <v>91277</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3160,25 +3160,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221725</v>
+        <v>67</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3188,10 +3188,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>375571</v>
+        <v>375498</v>
       </c>
       <c r="R26" t="n">
-        <v>6932464</v>
+        <v>6932458</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3250,10 +3250,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120494414</v>
+        <v>120493849</v>
       </c>
       <c r="B27" t="n">
-        <v>91277</v>
+        <v>105017</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3262,25 +3262,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>67</v>
+        <v>221725</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>375498</v>
+        <v>375571</v>
       </c>
       <c r="R27" t="n">
-        <v>6932458</v>
+        <v>6932464</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3454,10 +3454,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120493081</v>
+        <v>120495391</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3470,37 +3470,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>375570</v>
+        <v>375548</v>
       </c>
       <c r="R29" t="n">
-        <v>6932549</v>
+        <v>6932525</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3530,11 +3535,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3549,22 +3549,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120495316</v>
+        <v>120493081</v>
       </c>
       <c r="B30" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3577,21 +3577,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>375540</v>
+        <v>375570</v>
       </c>
       <c r="R30" t="n">
-        <v>6932499</v>
+        <v>6932549</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3637,6 +3637,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i området.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3651,22 +3656,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120495401</v>
+        <v>120495316</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3679,21 +3684,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3703,13 +3708,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>375558</v>
+        <v>375540</v>
       </c>
       <c r="R31" t="n">
-        <v>6932484</v>
+        <v>6932499</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3753,22 +3758,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120495391</v>
+        <v>120495401</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3781,42 +3786,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lillhammarsvallen, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>375548</v>
+        <v>375558</v>
       </c>
       <c r="R32" t="n">
-        <v>6932525</v>
+        <v>6932484</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3860,12 +3860,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
